--- a/artfynd/A 1482-2026 artfynd.xlsx
+++ b/artfynd/A 1482-2026 artfynd.xlsx
@@ -2146,7 +2146,7 @@
         <v>131121921</v>
       </c>
       <c r="B17" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>131121920</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>131122018</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 1482-2026 artfynd.xlsx
+++ b/artfynd/A 1482-2026 artfynd.xlsx
@@ -2146,7 +2146,7 @@
         <v>131121921</v>
       </c>
       <c r="B17" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>131121920</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>131122018</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 1482-2026 artfynd.xlsx
+++ b/artfynd/A 1482-2026 artfynd.xlsx
@@ -2252,7 +2252,7 @@
         <v>131121920</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>131122018</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 1482-2026 artfynd.xlsx
+++ b/artfynd/A 1482-2026 artfynd.xlsx
@@ -2146,7 +2146,7 @@
         <v>131121921</v>
       </c>
       <c r="B17" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>131121920</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>131122018</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 1482-2026 artfynd.xlsx
+++ b/artfynd/A 1482-2026 artfynd.xlsx
@@ -2146,7 +2146,7 @@
         <v>131121921</v>
       </c>
       <c r="B17" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>131121920</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>131122018</v>
       </c>
       <c r="B19" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 1482-2026 artfynd.xlsx
+++ b/artfynd/A 1482-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130834406</v>
+        <v>130834376</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424511</v>
+        <v>424488</v>
       </c>
       <c r="R2" t="n">
-        <v>6711373</v>
+        <v>6711452</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130834393</v>
+        <v>130834377</v>
       </c>
       <c r="B3" t="n">
-        <v>92268</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424513</v>
+        <v>424489</v>
       </c>
       <c r="R3" t="n">
-        <v>6711373</v>
+        <v>6711391</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -851,29 +851,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130834381</v>
+        <v>130834378</v>
       </c>
       <c r="B4" t="n">
-        <v>91809</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>424485</v>
+        <v>424513</v>
       </c>
       <c r="R4" t="n">
-        <v>6711319</v>
+        <v>6711372</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -955,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130834396</v>
+        <v>130834379</v>
       </c>
       <c r="B5" t="n">
-        <v>92268</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>424484</v>
+        <v>424508</v>
       </c>
       <c r="R5" t="n">
-        <v>6711318</v>
+        <v>6711376</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1046,51 +1045,50 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130834375</v>
+        <v>130834380</v>
       </c>
       <c r="B6" t="n">
-        <v>91772</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1100,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424498</v>
+        <v>424490</v>
       </c>
       <c r="R6" t="n">
-        <v>6711351</v>
+        <v>6711347</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1150,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130834394</v>
+        <v>130834381</v>
       </c>
       <c r="B7" t="n">
-        <v>92268</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1197,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424506</v>
+        <v>424485</v>
       </c>
       <c r="R7" t="n">
-        <v>6711370</v>
+        <v>6711319</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1241,29 +1239,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130834377</v>
+        <v>131887829</v>
       </c>
       <c r="B8" t="n">
-        <v>91809</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,7 +1295,7 @@
         <v>424489</v>
       </c>
       <c r="R8" t="n">
-        <v>6711391</v>
+        <v>6711289</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1325,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1345,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130834387</v>
+        <v>131887830</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1368,42 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>424517</v>
+        <v>424494</v>
       </c>
       <c r="R9" t="n">
-        <v>6711378</v>
+        <v>6711364</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1430,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1450,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130834376</v>
+        <v>131887831</v>
       </c>
       <c r="B10" t="n">
-        <v>91809</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>424488</v>
+        <v>424484</v>
       </c>
       <c r="R10" t="n">
-        <v>6711452</v>
+        <v>6711401</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1527,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1547,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130834378</v>
+        <v>131887832</v>
       </c>
       <c r="B11" t="n">
-        <v>91809</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>424513</v>
+        <v>424459</v>
       </c>
       <c r="R11" t="n">
-        <v>6711372</v>
+        <v>6711385</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1624,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1644,44 +1633,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130834395</v>
+        <v>131887833</v>
       </c>
       <c r="B12" t="n">
-        <v>92268</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1691,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424495</v>
+        <v>424454</v>
       </c>
       <c r="R12" t="n">
-        <v>6711339</v>
+        <v>6711387</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1721,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1735,29 +1724,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130834392</v>
+        <v>131887911</v>
       </c>
       <c r="B13" t="n">
-        <v>92268</v>
+        <v>91988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1765,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,7 +1780,7 @@
         <v>424488</v>
       </c>
       <c r="R13" t="n">
-        <v>6711452</v>
+        <v>6711360</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1819,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1833,29 +1821,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130834379</v>
+        <v>130834392</v>
       </c>
       <c r="B14" t="n">
-        <v>91809</v>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>424508</v>
+        <v>424488</v>
       </c>
       <c r="R14" t="n">
-        <v>6711376</v>
+        <v>6711452</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1931,28 +1918,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130834380</v>
+        <v>130834393</v>
       </c>
       <c r="B15" t="n">
-        <v>91809</v>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1960,21 +1948,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1984,10 +1972,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>424490</v>
+        <v>424513</v>
       </c>
       <c r="R15" t="n">
-        <v>6711347</v>
+        <v>6711373</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2028,50 +2016,51 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130834374</v>
+        <v>130834394</v>
       </c>
       <c r="B16" t="n">
-        <v>91772</v>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>424489</v>
+        <v>424506</v>
       </c>
       <c r="R16" t="n">
-        <v>6711391</v>
+        <v>6711370</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2125,67 +2114,64 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131121921</v>
+        <v>130834395</v>
       </c>
       <c r="B17" t="n">
-        <v>57080</v>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>424453</v>
+        <v>424495</v>
       </c>
       <c r="R17" t="n">
-        <v>6711513</v>
+        <v>6711339</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2212,17 +2198,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2st skrämdes upp ur skogen när jag passerade</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2231,28 +2212,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131121920</v>
+        <v>130834396</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>92369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2260,42 +2242,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>424416</v>
+        <v>424484</v>
       </c>
       <c r="R18" t="n">
-        <v>6711366</v>
+        <v>6711318</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2322,12 +2296,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2336,28 +2310,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131122018</v>
+        <v>131887872</v>
       </c>
       <c r="B19" t="n">
-        <v>57897</v>
+        <v>92406</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2365,42 +2340,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>424425</v>
+        <v>424461</v>
       </c>
       <c r="R19" t="n">
-        <v>6711334</v>
+        <v>6711381</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2427,17 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gammalt bohål 2m upp i gran</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2452,26 +2414,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131887872</v>
+        <v>131887874</v>
       </c>
       <c r="B20" t="n">
-        <v>92358</v>
+        <v>92406</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2499,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>424461</v>
+        <v>424486</v>
       </c>
       <c r="R20" t="n">
-        <v>6711381</v>
+        <v>6711304</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2561,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131887832</v>
+        <v>131887875</v>
       </c>
       <c r="B21" t="n">
-        <v>91898</v>
+        <v>92406</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2572,21 +2534,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2596,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>424459</v>
+        <v>424488</v>
       </c>
       <c r="R21" t="n">
-        <v>6711385</v>
+        <v>6711398</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2658,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131887833</v>
+        <v>131887876</v>
       </c>
       <c r="B22" t="n">
-        <v>91898</v>
+        <v>92406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2669,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2693,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>424454</v>
+        <v>424459</v>
       </c>
       <c r="R22" t="n">
-        <v>6711387</v>
+        <v>6711386</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2755,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131887875</v>
+        <v>130834374</v>
       </c>
       <c r="B23" t="n">
-        <v>92358</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2790,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>424488</v>
+        <v>424489</v>
       </c>
       <c r="R23" t="n">
-        <v>6711398</v>
+        <v>6711391</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2820,12 +2782,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2852,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131887911</v>
+        <v>130834375</v>
       </c>
       <c r="B24" t="n">
-        <v>91912</v>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2887,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>424488</v>
+        <v>424498</v>
       </c>
       <c r="R24" t="n">
-        <v>6711360</v>
+        <v>6711351</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2917,12 +2879,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2949,53 +2911,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131887859</v>
+        <v>130834406</v>
       </c>
       <c r="B25" t="n">
-        <v>57946</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>424456</v>
+        <v>424511</v>
       </c>
       <c r="R25" t="n">
-        <v>6711389</v>
+        <v>6711373</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3022,12 +2976,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3054,45 +3008,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131887876</v>
+        <v>131887859</v>
       </c>
       <c r="B26" t="n">
-        <v>92358</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>424459</v>
+        <v>424456</v>
       </c>
       <c r="R26" t="n">
-        <v>6711386</v>
+        <v>6711389</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3151,10 +3113,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131887831</v>
+        <v>130834387</v>
       </c>
       <c r="B27" t="n">
-        <v>91898</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3162,34 +3124,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>424484</v>
+        <v>424517</v>
       </c>
       <c r="R27" t="n">
-        <v>6711401</v>
+        <v>6711378</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3216,12 +3186,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3248,10 +3218,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131887830</v>
+        <v>131121920</v>
       </c>
       <c r="B28" t="n">
-        <v>91898</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3259,34 +3229,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>424494</v>
+        <v>424416</v>
       </c>
       <c r="R28" t="n">
-        <v>6711364</v>
+        <v>6711366</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3313,12 +3291,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3342,6 +3320,222 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131122018</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>424425</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6711334</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gammalt bohål 2m upp i gran</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131121921</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>424453</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6711513</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2st skrämdes upp ur skogen när jag passerade</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1482-2026 artfynd.xlsx
+++ b/artfynd/A 1482-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834376</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834377</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834378</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834379</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834380</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834381</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887829</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887830</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887831</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887832</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887833</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887911</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834392</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2032,6 +2102,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834393</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2130,6 +2205,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834394</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2228,6 +2308,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834395</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834396</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887872</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887874</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887875</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887876</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834374</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834375</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834406</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3110,6 +3235,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887859</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3215,6 +3345,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130834387</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3320,6 +3455,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131121920</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3430,6 +3570,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131122018</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3536,8 +3681,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131121921</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>